--- a/Tools/LubanGenerator/Numeric/#NumericAffect.xlsx
+++ b/Tools/LubanGenerator/Numeric/#NumericAffect.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Rider\Project\ET\Tools\LubanGenerator\Numeric\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61CD4D3-BCA6-46A2-915A-FF513746950C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A3B698-7ADA-440E-AB62-5BD3ECD6FCFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3560" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6400" yWindow="2600" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,60 +39,60 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>案例 移动速度额外增加
+最大血量越高移动速度越快 反之</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>return 0;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只要等级变化
+正常肯定是升级
+就直接修改经验值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Affect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Formula</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>return A.AV + (A.N - A.O) * 2;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>当前最大血量改变时
 如果当前血量&gt;最大血量
 则当前血是修改为最大血量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>案例 移动速度额外增加
-最大血量越高移动速度越快 反之</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>return 0;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只要等级变化
-正常肯定是升级
-就直接修改经验值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Affect</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Formula</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Speed1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Level</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>return A.AV + (A.N - A.O) * 2;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -445,55 +445,55 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="D1" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="70" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="42" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
